--- a/df_procesado.xlsx
+++ b/df_procesado.xlsx
@@ -3477,11 +3477,7 @@
           <t>Supermercado  (Exito, Jumbo, Etc)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1200k</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -5399,11 +5395,7 @@
           <t>Tienda de Barrio</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>700k</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -6121,11 +6113,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1500k</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -15003,11 +14991,7 @@
           <t>Tienda de Barrio</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1700k</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -18605,11 +18589,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>500k</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -21487,11 +21467,7 @@
           <t xml:space="preserve">Plaza de mercado </t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>1.000.000</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -21729,11 +21705,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>1000k</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -22211,11 +22183,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>700k</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -23173,11 +23141,7 @@
           <t>Supermercado  (Exito, Jumbo, Etc)</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>1200k</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -23655,11 +23619,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>1000k</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -24377,11 +24337,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>600k</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>Adulto joven</t>
@@ -35179,11 +35135,7 @@
           <t>Supermercado  (Exito, Jumbo, Etc)</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>2000k</t>
-        </is>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -36381,11 +36333,7 @@
           <t>Supermercado  (Exito, Jumbo, Etc)</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>1000k</t>
-        </is>
-      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -37583,11 +37531,7 @@
           <t>Supermercado  (Exito, Jumbo, Etc)</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>1800k</t>
-        </is>
-      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>Joven</t>
@@ -39745,11 +39689,7 @@
           <t>Hard Discount  (D1, ARA, etc )</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>1500k</t>
-        </is>
-      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>Joven</t>

--- a/df_procesado.xlsx
+++ b/df_procesado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV201"/>
+  <dimension ref="A1:BU201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>cafar</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -763,30 +763,25 @@
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>suavizant</t>
+          <t>suavizante</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>suavizante</t>
+          <t>talco</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>talco</t>
+          <t>tú</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>tú</t>
+          <t>verdura</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
-        <is>
-          <t>verdura</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
         <is>
           <t>vino</t>
         </is>
@@ -1017,18 +1012,15 @@
         <v>1</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS2" t="n">
         <v>1</v>
       </c>
       <c r="BT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1257,18 +1249,15 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1508,9 +1497,6 @@
       <c r="BU4" t="n">
         <v>0</v>
       </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1748,9 +1734,6 @@
       <c r="BU5" t="n">
         <v>0</v>
       </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1988,9 +1971,6 @@
       <c r="BU6" t="n">
         <v>0</v>
       </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -2228,9 +2208,6 @@
       <c r="BU7" t="n">
         <v>0</v>
       </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -2457,18 +2434,15 @@
         <v>1</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2708,9 +2682,6 @@
       <c r="BU9" t="n">
         <v>0</v>
       </c>
-      <c r="BV9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -2937,18 +2908,15 @@
         <v>1</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS10" t="n">
         <v>1</v>
       </c>
       <c r="BT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3174,10 +3142,10 @@
         <v>1</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
@@ -3186,9 +3154,6 @@
         <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3428,9 +3393,6 @@
       <c r="BU12" t="n">
         <v>0</v>
       </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -3666,9 +3628,6 @@
       <c r="BU13" t="n">
         <v>0</v>
       </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -3906,9 +3865,6 @@
       <c r="BU14" t="n">
         <v>0</v>
       </c>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -4138,15 +4094,12 @@
         <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4386,9 +4339,6 @@
       <c r="BU16" t="n">
         <v>0</v>
       </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -4615,18 +4565,15 @@
         <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
         <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4855,18 +4802,15 @@
         <v>1</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS18" t="n">
         <v>1</v>
       </c>
       <c r="BT18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5106,9 +5050,6 @@
       <c r="BU19" t="n">
         <v>0</v>
       </c>
-      <c r="BV19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -5338,15 +5279,12 @@
         <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5584,9 +5522,6 @@
       <c r="BU21" t="n">
         <v>0</v>
       </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -5824,9 +5759,6 @@
       <c r="BU22" t="n">
         <v>0</v>
       </c>
-      <c r="BV22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -6064,9 +5996,6 @@
       <c r="BU23" t="n">
         <v>0</v>
       </c>
-      <c r="BV23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -6087,7 +6016,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6291,18 +6220,15 @@
         <v>1</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS24" t="n">
         <v>1</v>
       </c>
       <c r="BT24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6531,18 +6457,15 @@
         <v>1</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS25" t="n">
         <v>1</v>
       </c>
       <c r="BT25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6565,7 +6488,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6771,18 +6694,15 @@
         <v>1</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT26" t="n">
         <v>0</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7022,9 +6942,6 @@
       <c r="BU27" t="n">
         <v>0</v>
       </c>
-      <c r="BV27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -7262,9 +7179,6 @@
       <c r="BU28" t="n">
         <v>0</v>
       </c>
-      <c r="BV28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -7285,7 +7199,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7500,9 +7414,6 @@
         <v>0</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7525,7 +7436,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -7740,9 +7651,6 @@
         <v>0</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7971,18 +7879,15 @@
         <v>1</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT31" t="n">
         <v>0</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8214,15 +8119,12 @@
         <v>0</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT32" t="n">
         <v>1</v>
       </c>
       <c r="BU32" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8451,18 +8353,15 @@
         <v>1</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT33" t="n">
         <v>0</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8691,18 +8590,15 @@
         <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
         <v>0</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8725,7 +8621,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -8931,18 +8827,15 @@
         <v>0</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT35" t="n">
         <v>0</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9171,18 +9064,15 @@
         <v>0</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT36" t="n">
         <v>0</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9411,18 +9301,15 @@
         <v>0</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT37" t="n">
         <v>0</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9445,7 +9332,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9660,9 +9547,6 @@
         <v>0</v>
       </c>
       <c r="BU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9902,9 +9786,6 @@
       <c r="BU39" t="n">
         <v>0</v>
       </c>
-      <c r="BV39" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -10134,15 +10015,12 @@
         <v>0</v>
       </c>
       <c r="BS40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10165,7 +10043,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -10380,9 +10258,6 @@
         <v>0</v>
       </c>
       <c r="BU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10611,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="BR42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS42" t="n">
         <v>0</v>
@@ -10620,9 +10495,6 @@
         <v>0</v>
       </c>
       <c r="BU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10854,15 +10726,12 @@
         <v>0</v>
       </c>
       <c r="BS43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11094,15 +10963,12 @@
         <v>0</v>
       </c>
       <c r="BS44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11334,15 +11200,12 @@
         <v>0</v>
       </c>
       <c r="BS45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11365,7 +11228,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11580,9 +11443,6 @@
         <v>0</v>
       </c>
       <c r="BU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11605,7 +11465,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11808,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="BQ47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR47" t="n">
         <v>1</v>
@@ -11817,12 +11677,9 @@
         <v>1</v>
       </c>
       <c r="BT47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12062,9 +11919,6 @@
       <c r="BU48" t="n">
         <v>0</v>
       </c>
-      <c r="BV48" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -12300,9 +12154,6 @@
         <v>0</v>
       </c>
       <c r="BU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12542,9 +12393,6 @@
       <c r="BU50" t="n">
         <v>0</v>
       </c>
-      <c r="BV50" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -12774,15 +12622,12 @@
         <v>0</v>
       </c>
       <c r="BS51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12805,7 +12650,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -13011,18 +12856,15 @@
         <v>1</v>
       </c>
       <c r="BR52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT52" t="n">
         <v>0</v>
       </c>
       <c r="BU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13262,9 +13104,6 @@
       <c r="BU53" t="n">
         <v>0</v>
       </c>
-      <c r="BV53" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -13491,18 +13330,15 @@
         <v>1</v>
       </c>
       <c r="BR54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT54" t="n">
         <v>0</v>
       </c>
       <c r="BU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13731,18 +13567,15 @@
         <v>0</v>
       </c>
       <c r="BR55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT55" t="n">
         <v>0</v>
       </c>
       <c r="BU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13765,7 +13598,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -13974,15 +13807,12 @@
         <v>0</v>
       </c>
       <c r="BS56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14005,7 +13835,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bogotá </t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -14211,18 +14041,15 @@
         <v>1</v>
       </c>
       <c r="BR57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT57" t="n">
         <v>0</v>
       </c>
       <c r="BU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14451,18 +14278,15 @@
         <v>0</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT58" t="n">
         <v>0</v>
       </c>
       <c r="BU58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14694,15 +14518,12 @@
         <v>0</v>
       </c>
       <c r="BS59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT59" t="n">
         <v>1</v>
       </c>
       <c r="BU59" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14940,9 +14761,6 @@
         <v>0</v>
       </c>
       <c r="BU60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15180,9 +14998,6 @@
       <c r="BU61" t="n">
         <v>0</v>
       </c>
-      <c r="BV61" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -15409,18 +15224,15 @@
         <v>0</v>
       </c>
       <c r="BR62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT62" t="n">
         <v>0</v>
       </c>
       <c r="BU62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15660,9 +15472,6 @@
       <c r="BU63" t="n">
         <v>0</v>
       </c>
-      <c r="BV63" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -15683,7 +15492,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15898,9 +15707,6 @@
         <v>0</v>
       </c>
       <c r="BU64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15923,7 +15729,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -16126,10 +15932,10 @@
         <v>0</v>
       </c>
       <c r="BQ65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS65" t="n">
         <v>0</v>
@@ -16138,9 +15944,6 @@
         <v>0</v>
       </c>
       <c r="BU65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16163,7 +15966,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -16378,9 +16181,6 @@
         <v>0</v>
       </c>
       <c r="BU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16609,18 +16409,15 @@
         <v>0</v>
       </c>
       <c r="BR67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT67" t="n">
         <v>0</v>
       </c>
       <c r="BU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16858,9 +16655,6 @@
         <v>0</v>
       </c>
       <c r="BU68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16883,7 +16677,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -17098,9 +16892,6 @@
         <v>0</v>
       </c>
       <c r="BU69" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17332,15 +17123,12 @@
         <v>0</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU70" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17572,15 +17360,12 @@
         <v>0</v>
       </c>
       <c r="BS71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU71" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17820,9 +17605,6 @@
       <c r="BU72" t="n">
         <v>0</v>
       </c>
-      <c r="BV72" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -17843,7 +17625,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>mani casanare</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -18058,9 +17840,6 @@
         <v>0</v>
       </c>
       <c r="BU73" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18083,7 +17862,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Boyaca</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -18298,9 +18077,6 @@
         <v>0</v>
       </c>
       <c r="BU74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18540,9 +18316,6 @@
       <c r="BU75" t="n">
         <v>0</v>
       </c>
-      <c r="BV75" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -18563,7 +18336,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -18776,9 +18549,6 @@
         <v>0</v>
       </c>
       <c r="BU76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18801,7 +18571,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -19016,9 +18786,6 @@
         <v>0</v>
       </c>
       <c r="BU77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19250,15 +19017,12 @@
         <v>0</v>
       </c>
       <c r="BS78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19281,7 +19045,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -19496,9 +19260,6 @@
         <v>0</v>
       </c>
       <c r="BU79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19738,9 +19499,6 @@
       <c r="BU80" t="n">
         <v>0</v>
       </c>
-      <c r="BV80" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -19978,9 +19736,6 @@
       <c r="BU81" t="n">
         <v>0</v>
       </c>
-      <c r="BV81" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -20001,7 +19756,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -20207,18 +19962,15 @@
         <v>0</v>
       </c>
       <c r="BR82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS82" t="n">
         <v>1</v>
       </c>
       <c r="BT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20458,9 +20210,6 @@
       <c r="BU83" t="n">
         <v>0</v>
       </c>
-      <c r="BV83" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -20698,9 +20447,6 @@
       <c r="BU84" t="n">
         <v>0</v>
       </c>
-      <c r="BV84" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -20927,18 +20673,15 @@
         <v>0</v>
       </c>
       <c r="BR85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT85" t="n">
         <v>0</v>
       </c>
       <c r="BU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20961,7 +20704,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -21167,18 +20910,15 @@
         <v>1</v>
       </c>
       <c r="BR86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21407,18 +21147,15 @@
         <v>0</v>
       </c>
       <c r="BR87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT87" t="n">
         <v>0</v>
       </c>
       <c r="BU87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21441,7 +21178,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -21654,9 +21391,6 @@
         <v>0</v>
       </c>
       <c r="BU88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21679,7 +21413,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -21883,18 +21617,15 @@
         <v>0</v>
       </c>
       <c r="BR89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS89" t="n">
         <v>1</v>
       </c>
       <c r="BT89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21917,7 +21648,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -22132,9 +21863,6 @@
         <v>0</v>
       </c>
       <c r="BU90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22367,12 +22095,9 @@
         <v>0</v>
       </c>
       <c r="BT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22601,18 +22326,15 @@
         <v>0</v>
       </c>
       <c r="BR92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS92" t="n">
         <v>1</v>
       </c>
       <c r="BT92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22852,9 +22574,6 @@
       <c r="BU93" t="n">
         <v>0</v>
       </c>
-      <c r="BV93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -23084,15 +22803,12 @@
         <v>0</v>
       </c>
       <c r="BS94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23115,7 +22831,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -23322,15 +23038,12 @@
         <v>0</v>
       </c>
       <c r="BS95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23353,7 +23066,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -23556,21 +23269,18 @@
         <v>1</v>
       </c>
       <c r="BQ96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23593,7 +23303,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -23806,9 +23516,6 @@
         <v>0</v>
       </c>
       <c r="BU97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24048,9 +23755,6 @@
       <c r="BU98" t="n">
         <v>0</v>
       </c>
-      <c r="BV98" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -24071,7 +23775,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -24277,18 +23981,15 @@
         <v>0</v>
       </c>
       <c r="BR99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
         <v>0</v>
       </c>
       <c r="BU99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24526,9 +24227,6 @@
       <c r="BU100" t="n">
         <v>0</v>
       </c>
-      <c r="BV100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -24549,7 +24247,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>mani casanare</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -24764,9 +24462,6 @@
         <v>0</v>
       </c>
       <c r="BU101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25004,9 +24699,6 @@
         <v>0</v>
       </c>
       <c r="BU102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25235,18 +24927,15 @@
         <v>1</v>
       </c>
       <c r="BR103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT103" t="n">
         <v>0</v>
       </c>
       <c r="BU103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25486,9 +25175,6 @@
       <c r="BU104" t="n">
         <v>0</v>
       </c>
-      <c r="BV104" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -25715,18 +25401,15 @@
         <v>0</v>
       </c>
       <c r="BR105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS105" t="n">
         <v>1</v>
       </c>
       <c r="BT105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU105" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25958,15 +25641,12 @@
         <v>0</v>
       </c>
       <c r="BS106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU106" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26195,7 +25875,7 @@
         <v>1</v>
       </c>
       <c r="BR107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS107" t="n">
         <v>0</v>
@@ -26204,9 +25884,6 @@
         <v>0</v>
       </c>
       <c r="BU107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26446,9 +26123,6 @@
       <c r="BU108" t="n">
         <v>0</v>
       </c>
-      <c r="BV108" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -26686,9 +26360,6 @@
       <c r="BU109" t="n">
         <v>0</v>
       </c>
-      <c r="BV109" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -26926,9 +26597,6 @@
       <c r="BU110" t="n">
         <v>0</v>
       </c>
-      <c r="BV110" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -27166,9 +26834,6 @@
       <c r="BU111" t="n">
         <v>0</v>
       </c>
-      <c r="BV111" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -27406,9 +27071,6 @@
       <c r="BU112" t="n">
         <v>0</v>
       </c>
-      <c r="BV112" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -27646,9 +27308,6 @@
       <c r="BU113" t="n">
         <v>0</v>
       </c>
-      <c r="BV113" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -27886,9 +27545,6 @@
       <c r="BU114" t="n">
         <v>0</v>
       </c>
-      <c r="BV114" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -28115,24 +27771,21 @@
         <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT115" t="n">
         <v>0</v>
       </c>
       <c r="BU115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV115" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46137.43263888889</v>
+        <v>46129.43263888889</v>
       </c>
       <c r="B116" t="n">
         <v>19</v>
@@ -28364,15 +28017,12 @@
         <v>0</v>
       </c>
       <c r="BU116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV116" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46137.52083333334</v>
+        <v>46133.20863425926</v>
       </c>
       <c r="B117" t="n">
         <v>20</v>
@@ -28595,24 +28245,21 @@
         <v>0</v>
       </c>
       <c r="BR117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS117" t="n">
         <v>1</v>
       </c>
       <c r="BT117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV117" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46137.57986111111</v>
+        <v>46133.03142361111</v>
       </c>
       <c r="B118" t="n">
         <v>22</v>
@@ -28835,24 +28482,21 @@
         <v>0</v>
       </c>
       <c r="BR118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS118" t="n">
         <v>1</v>
       </c>
       <c r="BT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV118" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46137.77083333334</v>
+        <v>46129.34289351852</v>
       </c>
       <c r="B119" t="n">
         <v>21</v>
@@ -29075,24 +28719,21 @@
         <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT119" t="n">
         <v>0</v>
       </c>
       <c r="BU119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV119" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46137.95625</v>
+        <v>46126.90923611111</v>
       </c>
       <c r="B120" t="n">
         <v>21</v>
@@ -29315,24 +28956,21 @@
         <v>1</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT120" t="n">
         <v>0</v>
       </c>
       <c r="BU120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46138.32986111111</v>
+        <v>46132.70090277777</v>
       </c>
       <c r="B121" t="n">
         <v>21</v>
@@ -29555,24 +29193,21 @@
         <v>0</v>
       </c>
       <c r="BR121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS121" t="n">
         <v>1</v>
       </c>
       <c r="BT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46138.37916666667</v>
+        <v>46131.38503472223</v>
       </c>
       <c r="B122" t="n">
         <v>24</v>
@@ -29804,15 +29439,12 @@
         <v>0</v>
       </c>
       <c r="BU122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV122" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46138.44375</v>
+        <v>46128.44622685185</v>
       </c>
       <c r="B123" t="n">
         <v>18</v>
@@ -30044,15 +29676,12 @@
         <v>0</v>
       </c>
       <c r="BU123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46138.67708333334</v>
+        <v>46125.62491898148</v>
       </c>
       <c r="B124" t="n">
         <v>19</v>
@@ -30284,15 +29913,12 @@
         <v>0</v>
       </c>
       <c r="BU124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV124" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46138.74375</v>
+        <v>46130.38908564814</v>
       </c>
       <c r="B125" t="n">
         <v>21</v>
@@ -30524,15 +30150,12 @@
         <v>0</v>
       </c>
       <c r="BU125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV125" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46139.32152777778</v>
+        <v>46130.06747685185</v>
       </c>
       <c r="B126" t="n">
         <v>21</v>
@@ -30755,24 +30378,21 @@
         <v>1</v>
       </c>
       <c r="BR126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT126" t="n">
         <v>0</v>
       </c>
       <c r="BU126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV126" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46139.48194444444</v>
+        <v>46132.5066087963</v>
       </c>
       <c r="B127" t="n">
         <v>20</v>
@@ -30992,27 +30612,24 @@
         <v>0</v>
       </c>
       <c r="BQ127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR127" t="n">
         <v>1</v>
       </c>
       <c r="BS127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT127" t="n">
         <v>0</v>
       </c>
       <c r="BU127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV127" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46139.70416666667</v>
+        <v>46125.22790509259</v>
       </c>
       <c r="B128" t="n">
         <v>20</v>
@@ -31244,15 +30861,12 @@
         <v>0</v>
       </c>
       <c r="BU128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46139.73680555556</v>
+        <v>46132.36591435185</v>
       </c>
       <c r="B129" t="n">
         <v>20</v>
@@ -31484,15 +31098,12 @@
         <v>0</v>
       </c>
       <c r="BU129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV129" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46139.88402777778</v>
+        <v>46125.51842592593</v>
       </c>
       <c r="B130" t="n">
         <v>24</v>
@@ -31724,15 +31335,12 @@
         <v>0</v>
       </c>
       <c r="BU130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV130" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46140.31805555556</v>
+        <v>46127.13743055556</v>
       </c>
       <c r="B131" t="n">
         <v>21</v>
@@ -31964,15 +31572,12 @@
         <v>0</v>
       </c>
       <c r="BU131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46140.49444444444</v>
+        <v>46128.10515046296</v>
       </c>
       <c r="B132" t="n">
         <v>22</v>
@@ -32204,15 +31809,12 @@
         <v>0</v>
       </c>
       <c r="BU132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46140.69236111111</v>
+        <v>46128.93361111111</v>
       </c>
       <c r="B133" t="n">
         <v>25</v>
@@ -32435,24 +32037,21 @@
         <v>0</v>
       </c>
       <c r="BR133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS133" t="n">
         <v>1</v>
       </c>
       <c r="BT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV133" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46140.79166666666</v>
+        <v>46129.50864583333</v>
       </c>
       <c r="B134" t="n">
         <v>21</v>
@@ -32684,15 +32283,12 @@
         <v>0</v>
       </c>
       <c r="BU134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV134" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46141.32152777778</v>
+        <v>46131.69121527778</v>
       </c>
       <c r="B135" t="n">
         <v>20</v>
@@ -32915,24 +32511,21 @@
         <v>0</v>
       </c>
       <c r="BR135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS135" t="n">
         <v>1</v>
       </c>
       <c r="BT135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV135" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46141.58819444444</v>
+        <v>46131.7230324074</v>
       </c>
       <c r="B136" t="n">
         <v>21</v>
@@ -33158,21 +32751,18 @@
         <v>0</v>
       </c>
       <c r="BS136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV136" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46141.63888888889</v>
+        <v>46130.37670138889</v>
       </c>
       <c r="B137" t="n">
         <v>22</v>
@@ -33395,24 +32985,21 @@
         <v>0</v>
       </c>
       <c r="BR137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT137" t="n">
         <v>0</v>
       </c>
       <c r="BU137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46141.89166666667</v>
+        <v>46133.69920138889</v>
       </c>
       <c r="B138" t="n">
         <v>20</v>
@@ -33635,24 +33222,21 @@
         <v>1</v>
       </c>
       <c r="BR138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS138" t="n">
         <v>1</v>
       </c>
       <c r="BT138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU138" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV138" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46142.325</v>
+        <v>46126.18001157408</v>
       </c>
       <c r="B139" t="n">
         <v>20</v>
@@ -33884,15 +33468,12 @@
         <v>0</v>
       </c>
       <c r="BU139" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46142.42986111111</v>
+        <v>46128.94494212963</v>
       </c>
       <c r="B140" t="n">
         <v>18</v>
@@ -34115,24 +33696,21 @@
         <v>1</v>
       </c>
       <c r="BR140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT140" t="n">
         <v>0</v>
       </c>
       <c r="BU140" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46142.71319444444</v>
+        <v>46130.62953703704</v>
       </c>
       <c r="B141" t="n">
         <v>19</v>
@@ -34364,15 +33942,12 @@
         <v>0</v>
       </c>
       <c r="BU141" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46142.95138888889</v>
+        <v>46132.95328703704</v>
       </c>
       <c r="B142" t="n">
         <v>20</v>
@@ -34604,15 +34179,12 @@
         <v>0</v>
       </c>
       <c r="BU142" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV142" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46143.29652777778</v>
+        <v>46125.38636574074</v>
       </c>
       <c r="B143" t="n">
         <v>21</v>
@@ -34835,24 +34407,21 @@
         <v>0</v>
       </c>
       <c r="BR143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS143" t="n">
         <v>1</v>
       </c>
       <c r="BT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV143" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46143.41111111111</v>
+        <v>46133.2196412037</v>
       </c>
       <c r="B144" t="n">
         <v>20</v>
@@ -35084,15 +34653,12 @@
         <v>0</v>
       </c>
       <c r="BU144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV144" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46143.57569444444</v>
+        <v>46128.73039351852</v>
       </c>
       <c r="B145" t="n">
         <v>20</v>
@@ -35316,21 +34882,18 @@
         <v>0</v>
       </c>
       <c r="BS145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV145" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46143.64166666667</v>
+        <v>46128.35827546296</v>
       </c>
       <c r="B146" t="n">
         <v>22</v>
@@ -35562,15 +35125,12 @@
         <v>0</v>
       </c>
       <c r="BU146" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV146" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143.81319444445</v>
+        <v>46126.60878472222</v>
       </c>
       <c r="B147" t="n">
         <v>20</v>
@@ -35802,15 +35362,12 @@
         <v>0</v>
       </c>
       <c r="BU147" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143.82430555556</v>
+        <v>46132.85482638889</v>
       </c>
       <c r="B148" t="n">
         <v>20</v>
@@ -36039,18 +35596,15 @@
         <v>0</v>
       </c>
       <c r="BT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU148" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV148" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46144.33055555556</v>
+        <v>46126.92767361111</v>
       </c>
       <c r="B149" t="n">
         <v>23</v>
@@ -36282,15 +35836,12 @@
         <v>0</v>
       </c>
       <c r="BU149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV149" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46144.59652777778</v>
+        <v>46127.12459490741</v>
       </c>
       <c r="B150" t="n">
         <v>21</v>
@@ -36514,21 +36065,18 @@
         <v>0</v>
       </c>
       <c r="BS150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV150" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46144.7</v>
+        <v>46130.32681712963</v>
       </c>
       <c r="B151" t="n">
         <v>22</v>
@@ -36760,15 +36308,12 @@
         <v>0</v>
       </c>
       <c r="BU151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV151" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46144.88819444444</v>
+        <v>46125.44851851852</v>
       </c>
       <c r="B152" t="n">
         <v>20</v>
@@ -37000,15 +36545,12 @@
         <v>0</v>
       </c>
       <c r="BU152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV152" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46145.29930555556</v>
+        <v>46130.2783912037</v>
       </c>
       <c r="B153" t="n">
         <v>20</v>
@@ -37240,15 +36782,12 @@
         <v>0</v>
       </c>
       <c r="BU153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV153" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46145.48958333334</v>
+        <v>46125.49204861111</v>
       </c>
       <c r="B154" t="n">
         <v>20</v>
@@ -37474,21 +37013,18 @@
         <v>0</v>
       </c>
       <c r="BS154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV154" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46145.5375</v>
+        <v>46131.93534722222</v>
       </c>
       <c r="B155" t="n">
         <v>21</v>
@@ -37718,15 +37254,12 @@
         <v>0</v>
       </c>
       <c r="BU155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV155" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46145.77013888889</v>
+        <v>46131.26064814815</v>
       </c>
       <c r="B156" t="n">
         <v>18</v>
@@ -37949,7 +37482,7 @@
         <v>1</v>
       </c>
       <c r="BR156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS156" t="n">
         <v>0</v>
@@ -37958,15 +37491,12 @@
         <v>0</v>
       </c>
       <c r="BU156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV156" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46145.88611111111</v>
+        <v>46131.27376157408</v>
       </c>
       <c r="B157" t="n">
         <v>18</v>
@@ -38189,24 +37719,21 @@
         <v>0</v>
       </c>
       <c r="BR157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT157" t="n">
         <v>0</v>
       </c>
       <c r="BU157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV157" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146.31388888889</v>
+        <v>46130.32114583333</v>
       </c>
       <c r="B158" t="n">
         <v>20</v>
@@ -38438,15 +37965,12 @@
         <v>0</v>
       </c>
       <c r="BU158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146.54027777778</v>
+        <v>46130.10662037037</v>
       </c>
       <c r="B159" t="n">
         <v>21</v>
@@ -38672,21 +38196,18 @@
         <v>0</v>
       </c>
       <c r="BS159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV159" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46146.62083333333</v>
+        <v>46132.65798611111</v>
       </c>
       <c r="B160" t="n">
         <v>20</v>
@@ -38912,21 +38433,18 @@
         <v>0</v>
       </c>
       <c r="BS160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU160" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV160" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146.68541666667</v>
+        <v>46128.67321759259</v>
       </c>
       <c r="B161" t="n">
         <v>19</v>
@@ -39158,15 +38676,12 @@
         <v>0</v>
       </c>
       <c r="BU161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV161" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146.82847222222</v>
+        <v>46132.75850694445</v>
       </c>
       <c r="B162" t="n">
         <v>20</v>
@@ -39398,15 +38913,12 @@
         <v>0</v>
       </c>
       <c r="BU162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV162" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147.29861111111</v>
+        <v>46127.83885416666</v>
       </c>
       <c r="B163" t="n">
         <v>20</v>
@@ -39635,18 +39147,15 @@
         <v>0</v>
       </c>
       <c r="BT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU163" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV163" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147.50069444445</v>
+        <v>46129.86649305555</v>
       </c>
       <c r="B164" t="n">
         <v>19</v>
@@ -39870,21 +39379,18 @@
         <v>0</v>
       </c>
       <c r="BS164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV164" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147.7875</v>
+        <v>46126.62122685185</v>
       </c>
       <c r="B165" t="n">
         <v>20</v>
@@ -40107,24 +39613,21 @@
         <v>0</v>
       </c>
       <c r="BR165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT165" t="n">
         <v>0</v>
       </c>
       <c r="BU165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV165" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148.31805555556</v>
+        <v>46133.33509259259</v>
       </c>
       <c r="B166" t="n">
         <v>18</v>
@@ -40350,21 +39853,18 @@
         <v>0</v>
       </c>
       <c r="BS166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV166" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148.44305555556</v>
+        <v>46129.4462037037</v>
       </c>
       <c r="B167" t="n">
         <v>28</v>
@@ -40587,24 +40087,21 @@
         <v>1</v>
       </c>
       <c r="BR167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS167" t="n">
         <v>1</v>
       </c>
       <c r="BT167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV167" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46148.62708333333</v>
+        <v>46127.03684027777</v>
       </c>
       <c r="B168" t="n">
         <v>19</v>
@@ -40824,27 +40321,24 @@
         <v>0</v>
       </c>
       <c r="BQ168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR168" t="n">
         <v>1</v>
       </c>
       <c r="BS168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT168" t="n">
         <v>0</v>
       </c>
       <c r="BU168" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV168" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148.64375</v>
+        <v>46125.13734953704</v>
       </c>
       <c r="B169" t="n">
         <v>22</v>
@@ -41076,15 +40570,12 @@
         <v>0</v>
       </c>
       <c r="BU169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV169" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46148.69375</v>
+        <v>46133.87883101852</v>
       </c>
       <c r="B170" t="n">
         <v>18</v>
@@ -41316,15 +40807,12 @@
         <v>0</v>
       </c>
       <c r="BU170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV170" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46148.83263888889</v>
+        <v>46130.87490740741</v>
       </c>
       <c r="B171" t="n">
         <v>19</v>
@@ -41556,15 +41044,12 @@
         <v>0</v>
       </c>
       <c r="BU171" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV171" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46148.95208333333</v>
+        <v>46133.7780324074</v>
       </c>
       <c r="B172" t="n">
         <v>19</v>
@@ -41796,15 +41281,12 @@
         <v>0</v>
       </c>
       <c r="BU172" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV172" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46149.29375</v>
+        <v>46132.82959490741</v>
       </c>
       <c r="B173" t="n">
         <v>23</v>
@@ -42030,21 +41512,18 @@
         <v>1</v>
       </c>
       <c r="BS173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT173" t="n">
         <v>0</v>
       </c>
       <c r="BU173" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV173" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46149.38958333333</v>
+        <v>46132.3965625</v>
       </c>
       <c r="B174" t="n">
         <v>21</v>
@@ -42267,24 +41746,21 @@
         <v>1</v>
       </c>
       <c r="BR174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT174" t="n">
         <v>0</v>
       </c>
       <c r="BU174" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV174" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46149.60138888889</v>
+        <v>46130.08204861111</v>
       </c>
       <c r="B175" t="n">
         <v>30</v>
@@ -42516,15 +41992,12 @@
         <v>0</v>
       </c>
       <c r="BU175" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV175" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46149.63958333333</v>
+        <v>46126.85530092593</v>
       </c>
       <c r="B176" t="n">
         <v>19</v>
@@ -42756,15 +42229,12 @@
         <v>0</v>
       </c>
       <c r="BU176" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV176" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46149.67986111111</v>
+        <v>46128.62631944445</v>
       </c>
       <c r="B177" t="n">
         <v>22</v>
@@ -42990,21 +42460,18 @@
         <v>0</v>
       </c>
       <c r="BS177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT177" t="n">
         <v>1</v>
       </c>
       <c r="BU177" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV177" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46149.95</v>
+        <v>46129.59883101852</v>
       </c>
       <c r="B178" t="n">
         <v>19</v>
@@ -43236,15 +42703,12 @@
         <v>0</v>
       </c>
       <c r="BU178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV178" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46150.32777777778</v>
+        <v>46130.12208333334</v>
       </c>
       <c r="B179" t="n">
         <v>21</v>
@@ -43476,15 +42940,12 @@
         <v>0</v>
       </c>
       <c r="BU179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV179" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46150.3625</v>
+        <v>46127.68196759259</v>
       </c>
       <c r="B180" t="n">
         <v>20</v>
@@ -43707,24 +43168,21 @@
         <v>0</v>
       </c>
       <c r="BR180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT180" t="n">
         <v>0</v>
       </c>
       <c r="BU180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV180" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46150.64305555556</v>
+        <v>46126.01951388889</v>
       </c>
       <c r="B181" t="n">
         <v>24</v>
@@ -43950,21 +43408,18 @@
         <v>0</v>
       </c>
       <c r="BS181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV181" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46150.84236111111</v>
+        <v>46133.6565625</v>
       </c>
       <c r="B182" t="n">
         <v>19</v>
@@ -44196,15 +43651,12 @@
         <v>0</v>
       </c>
       <c r="BU182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV182" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46151.29722222222</v>
+        <v>46128.7625</v>
       </c>
       <c r="B183" t="n">
         <v>21</v>
@@ -44436,15 +43888,12 @@
         <v>0</v>
       </c>
       <c r="BU183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV183" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46151.35277777778</v>
+        <v>46131.81728009259</v>
       </c>
       <c r="B184" t="n">
         <v>24</v>
@@ -44664,10 +44113,10 @@
         <v>0</v>
       </c>
       <c r="BQ184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS184" t="n">
         <v>0</v>
@@ -44676,15 +44125,12 @@
         <v>0</v>
       </c>
       <c r="BU184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV184" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46151.59722222222</v>
+        <v>46133.73142361111</v>
       </c>
       <c r="B185" t="n">
         <v>22</v>
@@ -44916,15 +44362,12 @@
         <v>0</v>
       </c>
       <c r="BU185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV185" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46151.77638888889</v>
+        <v>46126.33021990741</v>
       </c>
       <c r="B186" t="n">
         <v>20</v>
@@ -45156,15 +44599,12 @@
         <v>0</v>
       </c>
       <c r="BU186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV186" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46152.34444444445</v>
+        <v>46133.32072916667</v>
       </c>
       <c r="B187" t="n">
         <v>20</v>
@@ -45181,7 +44621,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -45396,15 +44836,12 @@
         <v>0</v>
       </c>
       <c r="BU187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV187" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46152.54236111111</v>
+        <v>46130.65924768519</v>
       </c>
       <c r="B188" t="n">
         <v>21</v>
@@ -45421,7 +44858,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -45630,21 +45067,18 @@
         <v>0</v>
       </c>
       <c r="BS188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV188" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46152.76805555556</v>
+        <v>46130.99541666666</v>
       </c>
       <c r="B189" t="n">
         <v>22</v>
@@ -45661,7 +45095,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -45867,24 +45301,21 @@
         <v>0</v>
       </c>
       <c r="BR189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT189" t="n">
         <v>0</v>
       </c>
       <c r="BU189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV189" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46152.92847222222</v>
+        <v>46126.23616898148</v>
       </c>
       <c r="B190" t="n">
         <v>19</v>
@@ -46104,10 +45535,10 @@
         <v>1</v>
       </c>
       <c r="BQ190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS190" t="n">
         <v>0</v>
@@ -46116,15 +45547,12 @@
         <v>0</v>
       </c>
       <c r="BU190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV190" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46153.33263888889</v>
+        <v>46128.48074074074</v>
       </c>
       <c r="B191" t="n">
         <v>21</v>
@@ -46350,21 +45778,18 @@
         <v>0</v>
       </c>
       <c r="BS191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV191" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46153.53472222222</v>
+        <v>46130.16530092592</v>
       </c>
       <c r="B192" t="n">
         <v>20</v>
@@ -46587,24 +46012,21 @@
         <v>1</v>
       </c>
       <c r="BR192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT192" t="n">
         <v>0</v>
       </c>
       <c r="BU192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV192" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46153.81319444445</v>
+        <v>46130.45197916667</v>
       </c>
       <c r="B193" t="n">
         <v>19</v>
@@ -46621,7 +46043,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -46836,15 +46258,12 @@
         <v>0</v>
       </c>
       <c r="BU193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV193" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46154.32222222222</v>
+        <v>46130.89508101852</v>
       </c>
       <c r="B194" t="n">
         <v>22</v>
@@ -47076,15 +46495,12 @@
         <v>0</v>
       </c>
       <c r="BU194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV194" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46154.40347222222</v>
+        <v>46133.95997685185</v>
       </c>
       <c r="B195" t="n">
         <v>20</v>
@@ -47307,24 +46723,21 @@
         <v>0</v>
       </c>
       <c r="BR195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT195" t="n">
         <v>0</v>
       </c>
       <c r="BU195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV195" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46154.66736111111</v>
+        <v>46130.34578703704</v>
       </c>
       <c r="B196" t="n">
         <v>19</v>
@@ -47550,21 +46963,18 @@
         <v>0</v>
       </c>
       <c r="BS196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV196" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46154.78819444445</v>
+        <v>46131.7881712963</v>
       </c>
       <c r="B197" t="n">
         <v>20</v>
@@ -47581,7 +46991,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>mani casanare</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -47796,15 +47206,12 @@
         <v>0</v>
       </c>
       <c r="BU197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV197" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46154.94027777778</v>
+        <v>46131.10957175926</v>
       </c>
       <c r="B198" t="n">
         <v>19</v>
@@ -48036,15 +47443,12 @@
         <v>0</v>
       </c>
       <c r="BU198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV198" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46155.32013888889</v>
+        <v>46133.68673611111</v>
       </c>
       <c r="B199" t="n">
         <v>19</v>
@@ -48061,7 +47465,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -48276,15 +47680,12 @@
         <v>0</v>
       </c>
       <c r="BU199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV199" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46155.46319444444</v>
+        <v>46133.0987037037</v>
       </c>
       <c r="B200" t="n">
         <v>19</v>
@@ -48516,15 +47917,12 @@
         <v>0</v>
       </c>
       <c r="BU200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV200" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46155.62916666667</v>
+        <v>46129.78417824074</v>
       </c>
       <c r="B201" t="n">
         <v>25</v>
@@ -48756,9 +48154,6 @@
         <v>0</v>
       </c>
       <c r="BU201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV201" t="n">
         <v>0</v>
       </c>
     </row>

--- a/df_procesado.xlsx
+++ b/df_procesado.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -3442,7 +3442,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Adulto</t>
+          <t>31-60</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -5336,7 +5336,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -6045,7 +6045,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Adulto joven</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -14812,7 +14812,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Adulto joven</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M74" t="n">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -18365,7 +18365,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M77" t="n">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -19550,7 +19550,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M83" t="n">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -21207,7 +21207,7 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -21442,7 +21442,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -21914,7 +21914,7 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M91" t="n">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M94" t="n">
@@ -22860,7 +22860,7 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -23332,7 +23332,7 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M97" t="n">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -23806,7 +23806,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -24041,7 +24041,7 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Adulto joven</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -24515,7 +24515,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M105" t="n">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M109" t="n">
@@ -26411,7 +26411,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -26885,7 +26885,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -27122,7 +27122,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -27359,7 +27359,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M115" t="n">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M116" t="n">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M119" t="n">
@@ -28781,7 +28781,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -29729,7 +29729,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -30440,7 +30440,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -30914,7 +30914,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -31388,7 +31388,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -31625,7 +31625,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -31862,7 +31862,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -32099,7 +32099,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -32336,7 +32336,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -32810,7 +32810,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -33047,7 +33047,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -33521,7 +33521,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -33758,7 +33758,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -34232,7 +34232,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -34704,7 +34704,7 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -34941,7 +34941,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -35178,7 +35178,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -35415,7 +35415,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -35652,7 +35652,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -35887,7 +35887,7 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -36361,7 +36361,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -36598,7 +36598,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -36835,7 +36835,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -37070,7 +37070,7 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -37307,7 +37307,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -37544,7 +37544,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -37781,7 +37781,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -38018,7 +38018,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -38492,7 +38492,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -39201,7 +39201,7 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -39438,7 +39438,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -39912,7 +39912,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Adulto joven</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -40149,7 +40149,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -40386,7 +40386,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>Menor de 18</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -41097,7 +41097,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -41334,7 +41334,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -41571,7 +41571,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -41808,7 +41808,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Adulto joven</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -42045,7 +42045,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -42282,7 +42282,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -42756,7 +42756,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -42993,7 +42993,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -43230,7 +43230,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -43467,7 +43467,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -43704,7 +43704,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -43941,7 +43941,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -44178,7 +44178,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -44415,7 +44415,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -44652,7 +44652,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -44889,7 +44889,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -45126,7 +45126,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -45363,7 +45363,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -45600,7 +45600,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -45837,7 +45837,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -46074,7 +46074,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -46311,7 +46311,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -46548,7 +46548,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -46785,7 +46785,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -47022,7 +47022,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -47259,7 +47259,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -47733,7 +47733,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -47970,7 +47970,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Joven</t>
+          <t>18-25</t>
         </is>
       </c>
       <c r="M201" t="n">
